--- a/Tests/module03_test_cases.xlsx
+++ b/Tests/module03_test_cases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Module03" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Module03'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Module03'!$A$1:$L$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
     <font>
       <name val="Segoe UI"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
       <sz val="10"/>
     </font>
     <font>
@@ -109,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,19 +123,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,19 +509,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -525,40 +539,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Feature ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feature Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Objective</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ExpectedResult</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -577,25 +601,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>M03-F01</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Course / Subject Creation</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>Create New Subject Manually</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Verify that staff can create a new subject manually by choosing a batch and semester.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A and Semester 1 exist.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>SubjectName=Programming; Batch=PNV26A; Semester=Semester 1</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Academic Management;
 2. Click Create Subject;
@@ -604,54 +638,64 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Subject is created successfully. Success notification appears. 'Programming' belongs to PNV26A, Semester 1 in subject list.</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>TC-M03-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>M03-F01</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Course / Subject Creation</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Bulk Subject Creation via Valid CSV</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can create multiple subjects simultaneously by importing a valid CSV file.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A and Semester 1 exist.</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>CSV containing: SubjectName, Batch, Semester columns with 'Programming,PNV26A,Semester 1' and 'English,PNV26A,Semester 1'</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>1. Navigate to Academic Management;
 2. Click Import Subjects via CSV;
@@ -659,17 +703,17 @@
 4. Click Import</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Subjects are imported successfully. Message displays 'Imported 2 subjects'. Programming and English appear in subject list.</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F01</t>
         </is>
@@ -688,25 +732,35 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>M03-F01</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Course / Subject Creation</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Create Subject Fails due to Empty Subject Name</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Verify that the system blocks subject creation and warns if the subject name is empty.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SubjectName=Empty; Batch=PNV26A; Semester=Semester 1</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Academic Management;
 2. Click Create Subject;
@@ -715,54 +769,64 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Saving is blocked. Error message 'Subject Name is required' displays. Name field is highlighted in red.</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F01, Validation Rules</t>
         </is>
       </c>
     </row>
     <row r="5" ht="135" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>TC-M03-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>M03-F02</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Grade Entry Structure</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Single Student Grade Entry</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can input periodic and regular test grades for a specific student in a subject.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Programming subject of batch PNV26A exists. Student ST001 belongs to batch PNV26A.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>StudentID=ST001; Subject=Programming; KT_TX=7.5; DK1=8.0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>1. Open Academic Management and select subject 'Programming';
 2. Find student ST001 in grade list;
@@ -771,17 +835,17 @@
 5. Click Save</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Grades are saved successfully. Success message displays. '7.5' and '8.0' appear on ST001's grade row.</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F02</t>
         </is>
@@ -800,25 +864,35 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>Auto TBKT Calculation and Exam Eligibility (TBKT &gt;= 5.0)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Verify that the system automatically calculates average grade (TBKT) based on weighted formula and grants exam eligibility (Eligible = YES) if TBKT &gt;= 5.0.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Programming subject has 1 periodic test weight. Student ST001 has grades.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>KT_TX=7.0; DK1=8.0</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>1. Select subject 'Programming';
 2. Input KT_TX=7.0 and DK1=8.0 for ST001;
@@ -826,54 +900,64 @@
 4. Observe TBKT column and Eligible status for ST001</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>TBKT is calculated as 7.67 (formula: (7.0*1 + 8.0*2)/3 = 7.67). Exam eligibility displays 'YES'.</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="105" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>TC-M03-006</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Auto TBKT Calculation and Exam Ineligibility (TBKT &lt; 5.0)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Verify that the system automatically calculates TBKT and blocks exam eligibility (Eligible = NO) if TBKT &lt; 5.0.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Programming subject has 1 periodic test weight. Student ST002 has grades.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>KT_TX=3.0; DK1=5.0</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>1. Select subject 'Programming';
 2. Input KT_TX=3.0 and DK1=5.0 for ST002;
@@ -881,17 +965,17 @@
 4. Observe TBKT column and Eligible status for ST002</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>TBKT is calculated as 4.33 (formula: (3.0*1 + 5.0*2)/3 = 4.33). Exam eligibility displays 'NO'.</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F03</t>
         </is>
@@ -910,25 +994,35 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>Block Final Exam Grade Entry When Ineligible (TBKT &lt; 5.0)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Verify that final exam grade input is disabled and blocked for students with status Eligible = NO.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Student ST002 has TBKT = 4.33 (Eligible = NO) in Programming.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>TCK=6.0</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>1. Open Programming grade list;
 2. Locate final exam grade (TCK) cell for ST002;
@@ -936,54 +1030,64 @@
 4. Observe the UI</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>The TCK cell for ST002 is disabled (read-only). Hovering displays 'Not eligible for final exam'. Any backend save attempt returns validation error.</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F03, Business Rules 7.4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="105" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>TC-M03-008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Allow Final Exam Grade Entry When Eligible (TBKT &gt;= 5.0)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Verify that final exam grade input is enabled and saved successfully for students with status Eligible = YES.</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Student ST001 has TBKT = 7.67 (Eligible = YES) in Programming.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>TCK=8.5</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>1. Open Programming grade list;
 2. Locate final exam grade (TCK) cell for ST001;
@@ -991,17 +1095,17 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Grade input behaves normally. Final exam grade '8.5' is saved successfully in database and displayed in UI.</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F03, Business Rules 7.4</t>
         </is>
@@ -1020,79 +1124,99 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>Input Retake Exam Grade for Student</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Verify that staff can enter a retake exam grade (TLCK) manually and optionally for a student.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Student ST001 has a final exam grade (TCK) recorded.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>TLCK=7.0</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>1. Open Programming grade list;
 2. Click the retake exam grade (TLCK) cell for ST001;
 3. Enter '7.0' and click Save</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Retake grade is recorded successfully and displayed in student's grade row. Other grades remain intact.</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F03, Business Rules 7.2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="105" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>TC-M03-010</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>M03-F04</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Grade Upload via CSV</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Bulk Grade Upload via CSV (Overwrite Mode)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Verify that CSV grade import overwrites all existing grades of students in the subject with the new values.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Subject English has existing grades for ST001 (KT_TX=5.0) and ST002 (KT_TX=6.0).</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>CSV containing: StudentID, KT_TX, DK1. Rows: 'ST001,8.0,9.0' and 'ST002,7.5,8.0'</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>1. Select subject 'English';
 2. Click Upload Grades via CSV;
@@ -1100,17 +1224,17 @@
 4. Observe grade list</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Upload succeeds. Grades for ST001 update to KT_TX=8.0, DK1=9.0 (TBKT=8.67), and ST002 update to KT_TX=7.5, DK1=8.0 (TBKT=7.83). Old grades are overwritten.</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F04, Business Rules 7.5</t>
         </is>
@@ -1129,96 +1253,116 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>M03-F04</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Grade Upload via CSV</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>CSV Grade Upload with Blank Cells Clears Existing Grades</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Verify that blank cells in CSV file are interpreted as NULL/Empty and clear corresponding old grades.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Student ST001 has grades (KT_TX=8.0, DK1=9.0).</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>CSV row: ST001,,9.0 (empty KT_TX value between commas)</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>1. Select subject, click Upload Grades via CSV;
 2. Select CSV containing empty KT_TX for ST001;
 3. Confirm import</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Grade list is updated. Regular test grade (KT_TX) for ST001 (previously 8.0) is cleared/empty. DK1 remains 9.0.</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F04, CSV Import Rules 8</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>TC-M03-012</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>M03-F04</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Grade Upload via CSV</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>CSV Grade Upload Fails due to Missing StudentID Column</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>Verify that CSV grade import rejects files missing the StudentID column and does not modify any data.</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>CSV with KT_TX, DK1, TCK columns (no StudentID column)</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>1. Select subject, click Upload Grades via CSV;
 2. Select CSV missing StudentID column and upload;
 3. Observe error message</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>System rejects the CSV file and displays error: 'Missing required column StudentID'. No grades are modified.</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F04, Error Handling 10</t>
         </is>
@@ -1237,96 +1381,116 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>M03-F04</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Grade Upload via CSV</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>CSV Grade Upload Fails due to Decimal Comma Format (8,5)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Verify that decimal grades formatted with commas (e.g. 8,5) instead of dots (8.5) trigger error.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>CSV row: ST001,8,5,9.0 (or double quoted ST001,\8</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>5\"</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>9.0)"</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1. Click Upload Grades via CSV;
 2. Select CSV containing '8,5' for ST001;
 3. Observe response</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>System blocks import or warns of invalid decimal format requiring dot '.'. Grade is not saved incorrectly.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="75" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>TC-M03-014</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>M03-F04</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Grade Upload via CSV</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>CSV Grade Upload Fails due to Out of Range Grades (0-10)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Verify that grades outside the 0-10 scale in CSV are rejected.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>CSV row: ST001,11.0,8.0 (KT_TX = 11.0)</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>1. Click Upload Grades via CSV;
 2. Select CSV with invalid grade '11.0';
 3. Observe error message</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>System blocks import and displays validation error: 'Grade must be between 0 and 10.' at the corresponding row. No grades are saved.</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F04, Validation Rules 9</t>
         </is>
@@ -1345,79 +1509,99 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>M03-F07</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Manual GPA &amp; Letter Grade Entry</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>Manually Upload Semester GPA and Letter Grade via CSV</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Verify that final score, GPA, and letter grades can be manually imported from CSV and preserved without automatic recalculation.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Student ST001 has semester grade record.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>CSV with StudentID, FinalScore, GPA, LetterGrade. Row: ST001,8.5,3.6,A</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to GPA &amp; Letter Grade CSV import;
 2. Select CSV containing GPA=3.6 and LetterGrade=A for ST001;
 3. View ST001 semester transcript details</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>GPA=3.6 and LetterGrade=A are saved and displayed exactly. No auto-recalculations are performed on these fields.</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F07, Business Rules 7.7</t>
         </is>
       </c>
     </row>
     <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>TC-M03-016</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>M03-F05</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Subject Deletion</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Subject Deletion Confirmation and Grade Cleanup</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Verify that subject deletion requires confirmation and permanently purges all associated grades.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>English subject exists with grades entered for students.</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>1. Navigate to subject list;
 2. Click Delete icon next to English;
@@ -1425,17 +1609,17 @@
 4. Click Delete again, click Confirm/Delete; verify list and DB</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Cancel keeps subject and grades intact. Confirm deletes English from subject list. All associated student grades for English are permanently purged from database.</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F05, Subject Deletion 7.8</t>
         </is>
@@ -1454,25 +1638,35 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
+          <t>M03-F06</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>PDF Transcript Export</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
           <t>Export Single Student PDF Transcript</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Verify that staff can generate and download a formal PDF transcript containing academic info for a specific student.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Student ST001 has grades, GPA, and letter grades entered.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>StudentID=ST001</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>1. Open Student list or Export Transcripts page;
 2. Find student ST001;
@@ -1480,54 +1674,64 @@
 4. Open the downloaded PDF file</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>PDF downloaded successfully. Content displays ST001 info, list of subjects, grades, TBKT, GPA, and Letter Grade.</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F06</t>
         </is>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>TC-M03-018</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>M03-F06</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>PDF Transcript Export</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Bulk Export PDF Transcripts for Multiple Students</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Verify that staff can export transcripts in batch for selected students.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Multiple students in batch PNV26A have grades.</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Batch=PNV26A; Selected: ST001, ST002, ST003</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>1. Open Export Transcripts page;
 2. Select Batch PNV26A;
@@ -1535,17 +1739,17 @@
 4. Click Export Selected transcripts to PDF</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Export succeeds. A combined PDF file or ZIP file containing individual PDFs is downloaded.</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: M03-F06</t>
         </is>
@@ -1564,96 +1768,116 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>M03-F06</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PDF Transcript Export</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>Verify Grade Color Rules on Reports (Green, Orange, Red)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Verify that final grades (/10) are colored dynamically on reports according to specified ranges.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>ST001 final grade is 8.5; ST002 is 7.0; ST003 is 4.5.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>1. Open Batch Transcript report;
 2. Locate final grades for ST001, ST002, and ST003;
 3. Observe color of grades</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>ST001 final grade (8.5) is Green (🟢) (grade &gt;= 8.0). ST002 final grade (7.0) is Orange (🟡) (grade 5.5 - 7.9). ST003 final grade (4.5) is Red (🔴) (grade &lt; 5.5).</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: Grade Color Rules 5</t>
         </is>
       </c>
     </row>
     <row r="21" ht="75" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>TC-M03-020</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>M03-F06</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PDF Transcript Export</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Verify GPA Color Rules on Reports (Green, Orange, Red)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Verify that GPA scores (/4) are colored dynamically on reports according to specified ranges.</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>ST001 GPA is 3.6; ST002 GPA is 3.0; ST003 GPA is 1.8.</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>1. Open Batch Transcript report;
 2. Locate GPA scores for ST001, ST002, and ST003;
 3. Observe color of GPA</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>ST001 GPA (3.6) is Green (🟢) (GPA &gt;= 3.5). ST002 GPA (3.0) is Orange (🟡) (GPA 2.0 - 3.4). ST003 GPA (1.8) is Red (🔴) (GPA &lt; 2.0).</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: Grade Color Rules 5</t>
         </is>
@@ -1672,103 +1896,123 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>M03-SEC</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Access Control &amp; Security</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>Block Student Access to Academic Management</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Verify that a student user cannot access Academic Management features.</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>User logged in with student email student01@student.passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Email=student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>1. Sign in via Google OAuth with student account;
 2. Attempt direct URL navigation to Academic Management page;
 3. Observe result</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Access is blocked. 'Access Denied' message displays or user is redirected to student home page. Academic Management menu is hidden.</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: User Roles</t>
         </is>
       </c>
     </row>
     <row r="23" ht="105" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>TC-M03-022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Module 03</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Module 03</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>M03-F03</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Automatic TBKT Calculation</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>TBKT Calculation Independence with Varying Periodic Test Counts (n)</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Verify that TBKT formula calculates correctly for subjects with different numbers of periodic tests (n from 1 to 6).</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Subject A has 1 periodic test (DK1); Subject B has 3 periodic tests (DK1, DK2, DK3).</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Subject A: KT_TX=6.0; DK1=7.0. Subject B: KT_TX=6.0; DK1=7.0; DK2=8.0; DK3=9.0.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>1. Under Subject A, enter KT_TX=6.0 and DK1=7.0 for ST001, save;
 2. Under Subject B, enter KT_TX=6.0, DK1=7.0, DK2=8.0, DK3=9.0 for ST001, save;
 3. Compare TBKT scores for ST001</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Subject A TBKT is 6.67 (formula: (6.0*1 + 7.0*2)/3 = 6.67). Subject B TBKT is 7.71 (formula: (6.0*1 + 7.0*2 + 8.0*2 + 9.0*2)/7 = 7.71). Both are calculated independently and correctly.</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>Related Requirement: TBKT Calculation Formula</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:L23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>